--- a/Result/profitability/2718.xlsx
+++ b/Result/profitability/2718.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM71"/>
+  <dimension ref="A1:AM72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.52</v>
       </c>
       <c r="M2" t="n">
-        <v>6.7725</v>
+        <v>2.62625</v>
       </c>
       <c r="N2" t="n">
-        <v>60.6575</v>
+        <v>57.3075</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.59</v>
       </c>
       <c r="M3" t="n">
-        <v>2.69</v>
+        <v>2.595</v>
       </c>
       <c r="N3" t="n">
-        <v>53.71375</v>
+        <v>53.70874999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.17</v>
       </c>
       <c r="M4" t="n">
-        <v>2.60625</v>
+        <v>2.53125</v>
       </c>
       <c r="N4" t="n">
-        <v>48.9625</v>
+        <v>48.30249999999999</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.1</v>
       </c>
       <c r="M5" t="n">
-        <v>2.50875</v>
+        <v>1.45375</v>
       </c>
       <c r="N5" t="n">
-        <v>42.41</v>
+        <v>41.20375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>1.48375</v>
+        <v>0.71</v>
       </c>
       <c r="N6" t="n">
-        <v>37.245</v>
+        <v>36.1075</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.22</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7274999999999999</v>
+        <v>0.55375</v>
       </c>
       <c r="N7" t="n">
-        <v>31.46125</v>
+        <v>30.9825</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,13 +1391,13 @@
         <v>0.44</v>
       </c>
       <c r="M8" t="n">
-        <v>0.59875</v>
+        <v>0.28</v>
       </c>
       <c r="N8" t="n">
-        <v>27.29625</v>
+        <v>27.6675</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9399,6 +9399,133 @@
       </c>
       <c r="AM71" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2718</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>82</v>
+      </c>
+      <c r="D72" t="n">
+        <v>35</v>
+      </c>
+      <c r="E72" t="n">
+        <v>47</v>
+      </c>
+      <c r="F72" t="n">
+        <v>57.73</v>
+      </c>
+      <c r="G72" t="n">
+        <v>23</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>27.78%</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>40</v>
+      </c>
+      <c r="J72" t="n">
+        <v>63</v>
+      </c>
+      <c r="K72" t="n">
+        <v>7</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M72" t="n">
+        <v>6.717499999999999</v>
+      </c>
+      <c r="N72" t="n">
+        <v>64.19624999999999</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0</v>
+      </c>
+      <c r="S72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>0</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
+      </c>
+      <c r="V72" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W72" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="X72" t="n">
+        <v>-0.9695817490494296</v>
+      </c>
+      <c r="Y72" t="n">
+        <v>2.969999999999999</v>
+      </c>
+      <c r="Z72" t="n">
+        <v>0.05423666910153391</v>
+      </c>
+      <c r="AA72" t="n">
+        <v>-8.44</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>-0.9906103286384976</v>
+      </c>
+      <c r="AC72" t="n">
+        <v>-9.649999999999999</v>
+      </c>
+      <c r="AD72" t="n">
+        <v>-0.143217571979816</v>
+      </c>
+      <c r="AE72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI72" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK72" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL72" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM72" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
